--- a/ZR.Admin.WebApi/wwwroot/data.xlsx
+++ b/ZR.Admin.WebApi/wwwroot/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Mine\ZRAdmin\public\ZrAdminNet\ZR.Admin.WebApi\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042658AA-2FF5-4BB1-B887-BF66BA2486C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16355A5-36A2-4D71-9BA1-F6F61EF69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="849" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="849" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="755">
   <si>
     <t>系统管理</t>
   </si>
@@ -2358,10 +2358,6 @@
   </si>
   <si>
     <t>sqlDiffLog</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">	article/articleTopic</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2543,6 +2539,22 @@
   </si>
   <si>
     <t>https://www.izhaorui.cn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>article/articleTopic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>动态发布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/article/publishMoments</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>article/publishMoments</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4953,7 +4965,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E2" s="6">
         <v>0</v>
@@ -4968,7 +4980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S162"/>
+  <dimension ref="A1:S163"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.44140625" customWidth="1"/>
@@ -5026,7 +5038,7 @@
         <v>291</v>
       </c>
       <c r="O1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -5148,7 +5160,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C5" s="12">
         <v>0</v>
@@ -5157,7 +5169,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12">
@@ -5380,7 +5392,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C11" s="12">
         <v>0</v>
@@ -5394,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I11" s="12">
         <v>1</v>
@@ -5412,7 +5424,7 @@
         <v>504</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C12" s="12">
         <v>12</v>
@@ -5435,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
@@ -5448,7 +5460,7 @@
         <v>505</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C13" s="12">
         <v>12</v>
@@ -5471,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
@@ -5482,7 +5494,7 @@
         <v>506</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C14" s="12">
         <v>12</v>
@@ -5496,16 +5508,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="I14" s="12">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12">
+        <v>0</v>
+      </c>
+      <c r="K14" s="12" t="s">
         <v>710</v>
-      </c>
-      <c r="I14" s="12">
-        <v>0</v>
-      </c>
-      <c r="J14" s="12">
-        <v>0</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>711</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
@@ -5515,7 +5527,7 @@
         <v>507</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C15" s="12">
         <v>12</v>
@@ -5529,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="I15" s="12">
         <v>0</v>
@@ -5538,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
@@ -5582,7 +5594,7 @@
       </c>
       <c r="M16" s="12"/>
       <c r="N16" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -6500,7 +6512,7 @@
         <v>503</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C39" s="12">
         <v>100</v>
@@ -6514,16 +6526,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="I39" s="12">
+        <v>0</v>
+      </c>
+      <c r="J39" s="12">
+        <v>0</v>
+      </c>
+      <c r="K39" s="12" t="s">
         <v>702</v>
-      </c>
-      <c r="I39" s="12">
-        <v>0</v>
-      </c>
-      <c r="J39" s="12">
-        <v>0</v>
-      </c>
-      <c r="K39" s="12" t="s">
-        <v>703</v>
       </c>
       <c r="L39" s="12"/>
       <c r="M39" s="12"/>
@@ -10324,7 +10336,7 @@
         <v>681</v>
       </c>
       <c r="F145" s="19" t="s">
-        <v>700</v>
+        <v>751</v>
       </c>
       <c r="G145" s="18">
         <v>0</v>
@@ -10532,7 +10544,7 @@
         <v>1147</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C151" s="12">
         <v>3</v>
@@ -10541,10 +10553,10 @@
         <v>17</v>
       </c>
       <c r="E151" s="12" t="s">
+        <v>721</v>
+      </c>
+      <c r="F151" s="12" t="s">
         <v>722</v>
-      </c>
-      <c r="F151" s="12" t="s">
-        <v>723</v>
       </c>
       <c r="G151" s="12">
         <v>0</v>
@@ -10559,10 +10571,10 @@
         <v>0</v>
       </c>
       <c r="K151" s="12" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="L151" s="12" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="M151" s="12"/>
       <c r="N151" s="12"/>
@@ -10597,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="K152" s="12" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="12"/>
@@ -10633,7 +10645,7 @@
         <v>0</v>
       </c>
       <c r="K153" s="12" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="L153" s="12"/>
       <c r="M153" s="12"/>
@@ -10644,7 +10656,7 @@
         <v>13</v>
       </c>
       <c r="B154" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -10653,7 +10665,7 @@
         <v>50</v>
       </c>
       <c r="E154" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -10668,7 +10680,7 @@
         <v>0</v>
       </c>
       <c r="L154" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -10685,7 +10697,7 @@
         <v>129</v>
       </c>
       <c r="B155" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C155">
         <v>13</v>
@@ -10694,10 +10706,10 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
+        <v>731</v>
+      </c>
+      <c r="F155" t="s">
         <v>732</v>
-      </c>
-      <c r="F155" t="s">
-        <v>733</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -10712,10 +10724,10 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
+        <v>733</v>
+      </c>
+      <c r="L155" t="s">
         <v>734</v>
-      </c>
-      <c r="L155" t="s">
-        <v>735</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -10753,7 +10765,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -10791,7 +10803,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -10829,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -10867,7 +10879,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -10884,7 +10896,7 @@
         <v>14</v>
       </c>
       <c r="B160" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C160">
         <v>2</v>
@@ -10893,10 +10905,10 @@
         <v>99</v>
       </c>
       <c r="E160" t="s">
+        <v>740</v>
+      </c>
+      <c r="F160" t="s">
         <v>741</v>
-      </c>
-      <c r="F160" t="s">
-        <v>742</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -10911,10 +10923,10 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
+        <v>742</v>
+      </c>
+      <c r="L160" t="s">
         <v>743</v>
-      </c>
-      <c r="L160" t="s">
-        <v>744</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -10931,7 +10943,7 @@
         <v>1167</v>
       </c>
       <c r="B161" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C161">
         <v>14</v>
@@ -10952,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -10969,7 +10981,7 @@
         <v>1168</v>
       </c>
       <c r="B162" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C162">
         <v>14</v>
@@ -10990,7 +11002,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -11001,6 +11013,46 @@
       <c r="S162" s="21">
         <v>46244.712049733796</v>
       </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A163" s="12">
+        <v>1069</v>
+      </c>
+      <c r="B163" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="C163" s="12">
+        <v>118</v>
+      </c>
+      <c r="D163" s="12">
+        <v>2</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>753</v>
+      </c>
+      <c r="F163" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="G163" s="12">
+        <v>0</v>
+      </c>
+      <c r="H163" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="I163" s="12">
+        <v>1</v>
+      </c>
+      <c r="J163" s="12">
+        <v>0</v>
+      </c>
+      <c r="K163" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="L163" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="M163" s="12"/>
+      <c r="N163" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A125" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -11274,7 +11326,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D7" s="9">
         <v>1</v>
@@ -11283,12 +11335,12 @@
         <v>484</v>
       </c>
       <c r="F7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -11297,7 +11349,7 @@
         <v>484</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
